--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Pyramid-Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF77AE2E-9233-4905-ACB5-5EDEEB63EB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4A96CC-B526-4A33-B0E2-E5CDC437E634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27214,16 +27214,16 @@
         <v>25</v>
       </c>
       <c r="G861" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H861" s="2">
-        <v>0</v>
+        <v>9.3518518518518525E-3</v>
       </c>
       <c r="I861" s="1">
         <v>46176.422106481485</v>
       </c>
       <c r="J861">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K861" t="s">
         <v>11</v>
@@ -27255,7 +27255,7 @@
         <v>46176.422800925924</v>
       </c>
       <c r="J862">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K862" t="s">
         <v>11</v>
@@ -27307,7 +27307,7 @@
         <v>25</v>
       </c>
       <c r="G864" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H864" s="2">
         <v>0</v>
@@ -27316,7 +27316,7 @@
         <v>46176.422800925924</v>
       </c>
       <c r="J864">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K864" t="s">
         <v>11</v>
@@ -27348,7 +27348,7 @@
         <v>46176.423495370371</v>
       </c>
       <c r="J865">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K865" t="s">
         <v>11</v>
@@ -27371,7 +27371,7 @@
         <v>25</v>
       </c>
       <c r="G866" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H866" s="2">
         <v>0</v>
@@ -27380,7 +27380,7 @@
         <v>46176.423495370371</v>
       </c>
       <c r="J866">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K866" t="s">
         <v>11</v>
@@ -27412,7 +27412,7 @@
         <v>46176.424189814818</v>
       </c>
       <c r="J867">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K867" t="s">
         <v>11</v>
@@ -27476,7 +27476,7 @@
         <v>46176.424189814818</v>
       </c>
       <c r="J869">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K869" t="s">
         <v>11</v>
@@ -27499,16 +27499,16 @@
         <v>25</v>
       </c>
       <c r="G870" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H870">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H870" s="2">
+        <v>9.780092592592592E-3</v>
       </c>
       <c r="I870" s="1">
         <v>46176.424884259257</v>
       </c>
       <c r="J870">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K870" t="s">
         <v>11</v>
@@ -27537,7 +27537,7 @@
         <v>46176.424884259257</v>
       </c>
       <c r="J871">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K871" t="s">
         <v>11</v>
@@ -27569,7 +27569,7 @@
         <v>46176.425578703704</v>
       </c>
       <c r="J872">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K872" t="s">
         <v>11</v>
